--- a/ci-cd-merge-resolver/repoCollector/datasets/YCSB.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/YCSB.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -42,6 +42,24 @@
   </si>
   <si>
     <t>isMultiModule</t>
+  </si>
+  <si>
+    <t>cd5e9d6f5e4d16b4fe6a115f87adf333bcd3f35b</t>
+  </si>
+  <si>
+    <t>45e8f7373e081d50f3aa73f26861f11dcb423058</t>
+  </si>
+  <si>
+    <t>4c14276573a6e2894d851bc2fe5aba16660ecea5</t>
+  </si>
+  <si>
+    <t>675b0fd0219e68c9497c7e21a68c8fa99902561f</t>
+  </si>
+  <si>
+    <t>5652511c59221d1d5573c6c5edb8461ed6254c41</t>
+  </si>
+  <si>
+    <t>9fc8b68df174750a8b8f359be940528ca1a8bd05</t>
   </si>
   <si>
     <t>c99a7e4a595a54f5223ad14ace5ceade9f7cd55c</t>
@@ -95,7 +113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -141,25 +159,89 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>60.0</v>
+        <v>37.0</v>
       </c>
       <c r="E2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G2" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>2.0460000038146973</v>
+      </c>
+      <c r="J2" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>31.743000030517578</v>
+      </c>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>104.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
         <v>3.0</v>
       </c>
-      <c r="F2" t="n" s="0">
+      <c r="F4" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="G2" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H2" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n" s="0">
-        <v>6.09499979019165</v>
-      </c>
-      <c r="J2" t="b" s="0">
-        <v>1</v>
+      <c r="G4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>20.93000030517578</v>
+      </c>
+      <c r="J4" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
